--- a/output/【河洛話注音】京口北固亭懷古.xlsx
+++ b/output/【河洛話注音】京口北固亭懷古.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33757A1-1E13-40AE-9E3D-D55A9E8C6CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6377B23-5188-4468-8A17-1025BA61737A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
+    <workbookView xWindow="-22020" yWindow="2235" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
   </bookViews>
   <sheets>
     <sheet name="閩拼拼音" sheetId="45" r:id="rId1"/>

--- a/output/【河洛話注音】京口北固亭懷古.xlsx
+++ b/output/【河洛話注音】京口北固亭懷古.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0120BAC1-F470-4424-A1CA-AB651981B520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEC4E11-D487-4610-87D3-1F5FEA138127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5475" yWindow="2130" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
   </bookViews>
   <sheets>
     <sheet name="閩拼拼音" sheetId="45" r:id="rId1"/>
@@ -1773,1520 +1773,1520 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4</t>
+    <t>&lt;div class='fifteen_yin'&gt;&lt;p class='title'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍七語&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;經四邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/p&gt;&lt;p class='author'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居二邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍二英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居二去&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;高二地&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍七地&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠二門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;觀七門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠一求&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居三時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭一喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;高二喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;君八喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居五時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠二喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;迦二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居二英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div class='Piau_Im'&gt;&lt;p class='title'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄥˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆣㄨ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;京&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧㄥ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧㆻ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;固&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;亭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㄞˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;古&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;江&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄤ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;山&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄢ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄥ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;無&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;覓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄧㆻ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;孫&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨㄣ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;仲&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㆲ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;舞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;榭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄚ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;歌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄜ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;流&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尋&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆬˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;巷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄤ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄧㆻ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;人&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆢㄧㄣˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;寄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;奴&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆦˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;曾&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄐㄧㄥ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄨ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆲˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;當&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;年&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄢˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;金&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧㆬ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;戈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄜ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鐵&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄊㄧㄚㆵ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;氣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄊㄨㄣ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨㄢ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;里&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;如&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆢㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;虎&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆣㄨㄢˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄚ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狼&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;居&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;得&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㆻ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;皇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;顧&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;十&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆴ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;三&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㆰ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;中&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;記&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;州&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄐㄧㄨ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;路&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆦ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;可&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;堪&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㆰ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;回&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㆤˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;首&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㆵ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狸&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆵ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;片&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄆㄧㄢ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;神&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄣˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄚ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鼓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;誰&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;問&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨㄣ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;廉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㆰˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頗&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄆㄜ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;老&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;能&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㄢˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div class='pin_yin'&gt;&lt;p class='title'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;éng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;gū&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pek&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;eng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sîong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tū&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;síong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bá&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;boān&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ka&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;êng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sì&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îu&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hu̍t&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sî&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;há&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;it&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;a&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sía&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;í&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sîong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pik&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huâi&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;buān&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;guân&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huán&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ǐng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ggû&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bīk&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;īng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bǐ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kǐ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;síong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;dǒ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;dû&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǐong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbǎ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbûan&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;gā&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hīong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hǒ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hút&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hǎ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;īt&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǐa&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ǐ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;síong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;gu7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;京&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;king1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pik4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;固&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;亭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ting5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huai5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;古&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;江&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kang1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;山&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;san1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;無&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;覓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;孫&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sun1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;仲&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tiong7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;舞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bu2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;榭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sia7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;歌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;流&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;liu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;u2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尋&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sim5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;巷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hang7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;人&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;jin5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;to2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;寄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;奴&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;loo5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;曾&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cing1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tu7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siong2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;當&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;年&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lian5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;金&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kim1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;戈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鐵&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thiat4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ba2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;氣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khi3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thun1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;buan7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;里&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;li2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;如&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ji5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;虎&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hoo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;guan5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ka1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狼&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;long5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;居&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ki1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;得&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tik4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;皇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;顧&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;si3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;十&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sip8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;三&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sam1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;中&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tiong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;記&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ho2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;州&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ciu1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;路&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;loo7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;可&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kho2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;堪&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kham1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;回&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hue5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;首&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siu2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hut8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狸&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;li5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;si5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ha2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;it4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;片&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;phian3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;神&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sin5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;a1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sia2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鼓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;誰&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sui5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;問&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bun7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;廉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;liam5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頗&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pho1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;老&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;i2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;能&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ling5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huan2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div class='Siang_Pai'&gt;&lt;p class='title'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rt&gt;ing2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄥˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rt&gt;gu7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆣㄨ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;京&lt;/rb&gt;&lt;rt&gt;king1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧㄥ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rt&gt;pik4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧㆻ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;固&lt;/rb&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;亭&lt;/rb&gt;&lt;rt&gt;ting5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rt&gt;huai5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㄞˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;古&lt;/rb&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;江&lt;/rb&gt;&lt;rt&gt;kang1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄤ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;山&lt;/rb&gt;&lt;rt&gt;san1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄢ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rt&gt;ing1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄥ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;無&lt;/rb&gt;&lt;rt&gt;bu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;覓&lt;/rb&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄧㆻ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;孫&lt;/rb&gt;&lt;rt&gt;sun1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨㄣ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;仲&lt;/rb&gt;&lt;rt&gt;tiong7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㆲ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;舞&lt;/rb&gt;&lt;rt&gt;bu2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;榭&lt;/rb&gt;&lt;rt&gt;sia7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄚ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;歌&lt;/rb&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄜ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;流&lt;/rb&gt;&lt;rt&gt;liu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rt&gt;pi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rt&gt;u2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rt&gt;khi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尋&lt;/rb&gt;&lt;rt&gt;sim5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆬˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;巷&lt;/rb&gt;&lt;rt&gt;hang7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄤ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陌&lt;/rb&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄧㆻ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;人&lt;/rb&gt;&lt;rt&gt;jin5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆢㄧㄣˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rt&gt;to2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;寄&lt;/rb&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;奴&lt;/rb&gt;&lt;rt&gt;loo5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆦˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;曾&lt;/rb&gt;&lt;rt&gt;cing1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄐㄧㄥ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rt&gt;tu7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄨ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rt&gt;siong2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆲˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;當&lt;/rb&gt;&lt;rt&gt;tong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;年&lt;/rb&gt;&lt;rt&gt;lian5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄢˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;金&lt;/rb&gt;&lt;rt&gt;kim1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧㆬ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;戈&lt;/rb&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄜ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鐵&lt;/rb&gt;&lt;rt&gt;thiat4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄊㄧㄚㆵ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rt&gt;ba2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;氣&lt;/rb&gt;&lt;rt&gt;khi3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吞&lt;/rb&gt;&lt;rt&gt;thun1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄊㄨㄣ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rt&gt;buan7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨㄢ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;里&lt;/rb&gt;&lt;rt&gt;li2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;如&lt;/rb&gt;&lt;rt&gt;ji5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆢㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;虎&lt;/rb&gt;&lt;rt&gt;hoo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rt&gt;guan5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆣㄨㄢˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rt&gt;ka1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄚ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狼&lt;/rb&gt;&lt;rt&gt;long5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;居&lt;/rb&gt;&lt;rt&gt;ki1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rt&gt;ing5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;得&lt;/rb&gt;&lt;rt&gt;tik4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㆻ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;皇&lt;/rb&gt;&lt;rt&gt;hong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;顧&lt;/rb&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rt&gt;si3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;十&lt;/rb&gt;&lt;rt&gt;sip8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆴ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;三&lt;/rb&gt;&lt;rt&gt;sam1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㆰ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;中&lt;/rb&gt;&lt;rt&gt;tiong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rt&gt;iu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;記&lt;/rb&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rt&gt;ho2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;州&lt;/rb&gt;&lt;rt&gt;ciu1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄐㄧㄨ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;路&lt;/rb&gt;&lt;rt&gt;loo7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆦ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;可&lt;/rb&gt;&lt;rt&gt;kho2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;堪&lt;/rb&gt;&lt;rt&gt;kham1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㆰ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;回&lt;/rb&gt;&lt;rt&gt;hue5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㆤˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;首&lt;/rb&gt;&lt;rt&gt;siu2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rt&gt;hut8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㆵ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狸&lt;/rb&gt;&lt;rt&gt;li5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rt&gt;si5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rt&gt;ha2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rt&gt;it4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆵ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;片&lt;/rb&gt;&lt;rt&gt;phian3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄆㄧㄢ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;神&lt;/rb&gt;&lt;rt&gt;sin5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄣˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rt&gt;a1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄚ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rt&gt;sia2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鼓&lt;/rb&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;誰&lt;/rb&gt;&lt;rt&gt;sui5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;問&lt;/rb&gt;&lt;rt&gt;bun7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨㄣ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;廉&lt;/rb&gt;&lt;rt&gt;liam5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㆰˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頗&lt;/rb&gt;&lt;rt&gt;pho1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄆㄜ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;老&lt;/rb&gt;&lt;rt&gt;lo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rt&gt;i2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;能&lt;/rb&gt;&lt;rt&gt;ling5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rt&gt;huan2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㄢˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>chian1</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>cho2</t>
+  </si>
+  <si>
+    <t>chong1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄑㄧㄢ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄑㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㄨㄧ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhian&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhui&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshian&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshui&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chian1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chui1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cho2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rt&gt;chian1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄑㄧㄢ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rt&gt;chi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄑㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rt&gt;chui1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㄨㄧ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rt&gt;cho2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rt&gt;chong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>khoo2</t>
+  </si>
+  <si>
+    <t>miu5</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>thai1</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>tai5</t>
+  </si>
+  <si>
+    <t>cong2</t>
+  </si>
+  <si>
+    <t>ta2</t>
+  </si>
+  <si>
+    <t>sia5</t>
+  </si>
+  <si>
+    <t>hiong3</t>
+  </si>
+  <si>
+    <t>su1</t>
+  </si>
+  <si>
+    <t>bong7</t>
+  </si>
+  <si>
+    <t>ping5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;丩五毛&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠二地&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;經五邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;丩二喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆦㆻ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄇㄧㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄊㄞ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄗㆲˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄚˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lo̍k&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khó͘&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;m̂iu&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thai&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chóng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tá&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sîa&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pêng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;híu&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khóo&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tsóng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pîng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbniú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;dǎ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bíng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lok8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khoo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;miu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thai1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cong2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ta2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sia5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ping5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiu2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rt&gt;lok8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆦㆻ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rt&gt;khoo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rt&gt;miu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄇㄧㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rt&gt;thai1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄊㄞ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rt&gt;cong2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄗㆲˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rt&gt;ta2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rt&gt;sia5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄚˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rt&gt;ping5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rt&gt;hiu2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;公三喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭一喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;公七門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㆲ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㆲ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hòng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bōng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hīong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbông&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hong3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bong7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rt&gt;hong3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆲ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rt&gt;bong7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㆲ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【十五音切語】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t>&lt;div class='fifteen_yin'&gt;&lt;p class='title'&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍七語&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;經四邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t>&lt;/p&gt;&lt;p class='author'&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭一喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居二邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍二英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居二去&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;高二地&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍七地&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠二門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;觀七門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠一求&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居三時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭一喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;高二喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;君八喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居五時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠二喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;迦二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;居二英&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭五時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【方音符號注音】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t>&lt;div class='Piau_Im'&gt;&lt;p class='title'&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄥˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆣㄨ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;京&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧㄥ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧㆻ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;固&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;亭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㄞˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;古&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;江&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄤ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;山&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄢ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄥ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;無&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;覓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄧㆻ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;孫&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨㄣ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;仲&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㆲ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;舞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;榭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄚ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;歌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄜ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;流&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尋&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆬˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;巷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄤ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄧㆻ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;人&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆢㄧㄣˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;寄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;奴&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆦˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;曾&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄐㄧㄥ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄨ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆲˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;當&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;年&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄢˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;金&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧㆬ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;戈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄜ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鐵&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄊㄧㄚㆵ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;氣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄊㄨㄣ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨㄢ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;里&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;如&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆢㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;虎&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆣㄨㄢˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄚ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狼&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;居&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;得&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㆻ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;皇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;顧&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;十&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆴ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;三&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㆰ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;中&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄧㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;記&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㄧ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;州&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄐㄧㄨ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;路&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆦ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;可&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;堪&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㆰ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;回&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㆤˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;首&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㆵ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狸&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧㆵ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;片&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄆㄧㄢ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;神&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄣˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄚ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鼓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄍㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;誰&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨㄧˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;問&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄨㄣ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;廉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㆰˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頗&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄆㄜ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;老&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㆲˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;能&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄨㄢˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【白話字拼音】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t>&lt;div class='pin_yin'&gt;&lt;p class='title'&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;éng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;gū&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pek&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;eng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sîong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tū&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;síong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bá&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;boān&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ka&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;êng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sì&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bîong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îu&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hu̍t&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sî&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;há&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;it&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;a&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sía&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;í&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sîong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【台羅拼音】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pik&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huâi&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;buān&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;guân&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;îng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huán&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【閩拼標音】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ǐng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ggû&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bīk&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;īng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hīong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bǐ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kǐ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;síong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;dǒ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;dû&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǐong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbǎ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbûan&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;gā&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbíong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hīong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hǒ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;íong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hút&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hǎ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;īt&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǐa&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ǐ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;síong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【台羅改良式】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;gu7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;京&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;king1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pik4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;固&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;亭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ting5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huai5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;古&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;江&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kang1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;山&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;san1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;無&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;覓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;孫&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sun1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;仲&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tiong7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;舞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bu2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;榭&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sia7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;歌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;流&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;liu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;u2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尋&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sim5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;巷&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hang7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陌&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;人&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;jin5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;to2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;寄&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;奴&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;loo5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;曾&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cing1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tu7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siong2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;當&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;年&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lian5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;金&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kim1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;戈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鐵&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thiat4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ba2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;氣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khi3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吞&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thun1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;buan7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;里&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;li2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;如&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ji5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;虎&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hoo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;guan5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ka1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狼&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;long5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;居&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ki1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ing5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;得&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tik4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;皇&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;顧&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;si3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;十&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sip8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;三&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sam1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;biong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;中&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tiong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;記&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ho2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;州&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ciu1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;路&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;loo7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;可&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kho2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;堪&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;kham1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;回&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hue5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;首&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siu2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hut8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狸&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;li5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;si5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ha2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;it4&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;片&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;phian3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;神&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sin5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;a1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sia2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鼓&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;誰&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sui5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;問&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bun7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;廉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;liam5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頗&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pho1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;老&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;i2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;能&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ling5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;huan2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">《京口北固亭懷古》【雙排注音】
 &lt;div class='separator' style='clear: both'&gt;
   &lt;a href='圖片' style='display: block; padding: 1em 0; text-align: center'&gt;
     &lt;img alt='京口北固亭懷古' border='0' width='400' data-original-height='630' data-original-width='1200'
-      src='https://ccc1960.blogspot.com/2022/11/%E6%B0%B8%E9%81%87%E6%A8%82%C2%B7%E4%BA%AC%F3%A0%87%A1%E5%8F%A3%F3%A0%87%A2%E5%8C%97%F3%A0%87%A1%E5%9B%BA%E4%BA%AD%E6%87%B7%E5%8F%A4' /&gt;
+      src='https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg' /&gt;
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
-  </si>
-  <si>
-    <t>&lt;div class='Siang_Pai'&gt;&lt;p class='title'&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;永&lt;/rb&gt;&lt;rt&gt;ing2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄥˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;遇&lt;/rb&gt;&lt;rt&gt;gu7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆣㄨ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;京&lt;/rb&gt;&lt;rt&gt;king1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧㄥ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;北&lt;/rb&gt;&lt;rt&gt;pik4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧㆻ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;固&lt;/rb&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;亭&lt;/rb&gt;&lt;rt&gt;ting5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;懷&lt;/rb&gt;&lt;rt&gt;huai5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㄞˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;古&lt;/rb&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;江&lt;/rb&gt;&lt;rt&gt;kang1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄤ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;山&lt;/rb&gt;&lt;rt&gt;san1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄢ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;英&lt;/rb&gt;&lt;rt&gt;ing1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄥ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雄&lt;/rb&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;無&lt;/rb&gt;&lt;rt&gt;bu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;覓&lt;/rb&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄧㆻ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;孫&lt;/rb&gt;&lt;rt&gt;sun1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨㄣ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;仲&lt;/rb&gt;&lt;rt&gt;tiong7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㆲ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;舞&lt;/rb&gt;&lt;rt&gt;bu2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;榭&lt;/rb&gt;&lt;rt&gt;sia7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄚ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;歌&lt;/rb&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄜ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;流&lt;/rb&gt;&lt;rt&gt;liu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;被&lt;/rb&gt;&lt;rt&gt;pi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;雨&lt;/rb&gt;&lt;rt&gt;u2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;去&lt;/rb&gt;&lt;rt&gt;khi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陽&lt;/rb&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樹&lt;/rb&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尋&lt;/rb&gt;&lt;rt&gt;sim5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆬˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;常&lt;/rb&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;巷&lt;/rb&gt;&lt;rt&gt;hang7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄤ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;陌&lt;/rb&gt;&lt;rt&gt;bik8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄧㆻ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;人&lt;/rb&gt;&lt;rt&gt;jin5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆢㄧㄣˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;道&lt;/rb&gt;&lt;rt&gt;to2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;寄&lt;/rb&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;奴&lt;/rb&gt;&lt;rt&gt;loo5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆦˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;曾&lt;/rb&gt;&lt;rt&gt;cing1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄐㄧㄥ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;住&lt;/rb&gt;&lt;rt&gt;tu7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄨ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;想&lt;/rb&gt;&lt;rt&gt;siong2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆲˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;當&lt;/rb&gt;&lt;rt&gt;tong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;年&lt;/rb&gt;&lt;rt&gt;lian5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄢˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;金&lt;/rb&gt;&lt;rt&gt;kim1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧㆬ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;戈&lt;/rb&gt;&lt;rt&gt;ko1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄜ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鐵&lt;/rb&gt;&lt;rt&gt;thiat4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄊㄧㄚㆵ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;馬&lt;/rb&gt;&lt;rt&gt;ba2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;氣&lt;/rb&gt;&lt;rt&gt;khi3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吞&lt;/rb&gt;&lt;rt&gt;thun1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄊㄨㄣ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;萬&lt;/rb&gt;&lt;rt&gt;buan7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨㄢ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;里&lt;/rb&gt;&lt;rt&gt;li2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;如&lt;/rb&gt;&lt;rt&gt;ji5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆢㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;虎&lt;/rb&gt;&lt;rt&gt;hoo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;元&lt;/rb&gt;&lt;rt&gt;guan5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆣㄨㄢˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;嘉&lt;/rb&gt;&lt;rt&gt;ka1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄚ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狼&lt;/rb&gt;&lt;rt&gt;long5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;居&lt;/rb&gt;&lt;rt&gt;ki1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;贏&lt;/rb&gt;&lt;rt&gt;ing5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;得&lt;/rb&gt;&lt;rt&gt;tik4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㆻ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;皇&lt;/rb&gt;&lt;rt&gt;hong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;顧&lt;/rb&gt;&lt;rt&gt;koo3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;四&lt;/rb&gt;&lt;rt&gt;si3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;十&lt;/rb&gt;&lt;rt&gt;sip8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆴ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;三&lt;/rb&gt;&lt;rt&gt;sam1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㆰ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rt&gt;biong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;中&lt;/rb&gt;&lt;rt&gt;tiong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;猶&lt;/rb&gt;&lt;rt&gt;iu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;記&lt;/rb&gt;&lt;rt&gt;ki3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㄧ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;烽&lt;/rb&gt;&lt;rt&gt;hiong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;火&lt;/rb&gt;&lt;rt&gt;ho2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;揚&lt;/rb&gt;&lt;rt&gt;iong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;州&lt;/rb&gt;&lt;rt&gt;ciu1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄐㄧㄨ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;路&lt;/rb&gt;&lt;rt&gt;loo7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆦ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;可&lt;/rb&gt;&lt;rt&gt;kho2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;堪&lt;/rb&gt;&lt;rt&gt;kham1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㆰ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;回&lt;/rb&gt;&lt;rt&gt;hue5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㆤˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;首&lt;/rb&gt;&lt;rt&gt;siu2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;佛&lt;/rb&gt;&lt;rt&gt;hut8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㆵ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;狸&lt;/rb&gt;&lt;rt&gt;li5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;祠&lt;/rb&gt;&lt;rt&gt;si5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;下&lt;/rb&gt;&lt;rt&gt;ha2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;一&lt;/rb&gt;&lt;rt&gt;it4&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧㆵ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;片&lt;/rb&gt;&lt;rt&gt;phian3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄆㄧㄢ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;神&lt;/rb&gt;&lt;rt&gt;sin5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄣˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鴉&lt;/rb&gt;&lt;rt&gt;a1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄚ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;社&lt;/rb&gt;&lt;rt&gt;sia2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;鼓&lt;/rb&gt;&lt;rt&gt;koo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄍㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;誰&lt;/rb&gt;&lt;rt&gt;sui5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨㄧˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;問&lt;/rb&gt;&lt;rt&gt;bun7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄨㄣ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;廉&lt;/rb&gt;&lt;rt&gt;liam5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㆰˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頗&lt;/rb&gt;&lt;rt&gt;pho1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄆㄜ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;老&lt;/rb&gt;&lt;rt&gt;lo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;矣&lt;/rb&gt;&lt;rt&gt;i2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;尚&lt;/rb&gt;&lt;rt&gt;siong5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㆲˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;能&lt;/rb&gt;&lt;rt&gt;ling5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;飯&lt;/rb&gt;&lt;rt&gt;huan2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄨㄢˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t>chian1</t>
-  </si>
-  <si>
-    <t>ch</t>
-  </si>
-  <si>
-    <t>cho2</t>
-  </si>
-  <si>
-    <t>chong1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄑㄧㄢ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄑㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㄨㄧ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㄜˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㆲ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhian&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhui&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshian&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshui&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chian1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chui1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cho2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chong1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rt&gt;chian1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄑㄧㄢ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rt&gt;chi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄑㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rt&gt;chui1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㄨㄧ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;草&lt;/rb&gt;&lt;rt&gt;cho2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㄜˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;倉&lt;/rb&gt;&lt;rt&gt;chong1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㆲ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>khoo2</t>
-  </si>
-  <si>
-    <t>miu5</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>thai1</t>
-  </si>
-  <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t>tai5</t>
-  </si>
-  <si>
-    <t>cong2</t>
-  </si>
-  <si>
-    <t>ta2</t>
-  </si>
-  <si>
-    <t>sia5</t>
-  </si>
-  <si>
-    <t>hiong3</t>
-  </si>
-  <si>
-    <t>su1</t>
-  </si>
-  <si>
-    <t>bong7</t>
-  </si>
-  <si>
-    <t>ping5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;丩五毛&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;膠二地&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭三喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍一時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;經五邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;丩二喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㆦㆻ˙&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄎㆦˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄇㄧㄨˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄊㄞ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄗㆲˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄉㄚˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄒㄧㄚˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㆲ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lo̍k&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khó͘&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;m̂iu&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thai&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chóng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tá&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sîa&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hìong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;su&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pêng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;híu&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khóo&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tsóng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pîng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbniú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;dǎ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sū&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bíng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lok8&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;khoo2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;miu5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;thai1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cong2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ta2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sia5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiong3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;su1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ping5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hiu2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;樂&lt;/rb&gt;&lt;rt&gt;lok8&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㆦㆻ˙&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;口&lt;/rb&gt;&lt;rt&gt;khoo2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄎㆦˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;謀&lt;/rb&gt;&lt;rt&gt;miu5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄇㄧㄨˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;台&lt;/rb&gt;&lt;rt&gt;thai1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄊㄞ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;總&lt;/rb&gt;&lt;rt&gt;cong2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄗㆲˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;打&lt;/rb&gt;&lt;rt&gt;ta2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄚˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;斜&lt;/rb&gt;&lt;rt&gt;sia5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄒㄧㄚˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rt&gt;hiong3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㆲ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rt&gt;su1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;憑&lt;/rb&gt;&lt;rt&gt;ping5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;否&lt;/rb&gt;&lt;rt&gt;hiu2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
 </sst>
 </file>
@@ -4518,7 +4518,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -4557,7 +4557,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="C7" t="s">
         <v>124</v>
@@ -4692,10 +4692,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
       <c r="C16" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D16" t="s">
         <v>139</v>
@@ -4902,10 +4902,10 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="C28" t="s">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="D28" t="s">
         <v>160</v>
@@ -4925,7 +4925,7 @@
         <v>525</v>
       </c>
       <c r="C29" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D29" t="s">
         <v>118</v>
@@ -5012,13 +5012,13 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>991</v>
+        <v>971</v>
       </c>
       <c r="C35" t="s">
         <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>992</v>
+        <v>972</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -5037,16 +5037,16 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C37" t="s">
         <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -5077,7 +5077,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>994</v>
+        <v>974</v>
       </c>
       <c r="C39" t="s">
         <v>539</v>
@@ -5142,7 +5142,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>995</v>
+        <v>975</v>
       </c>
       <c r="C43" t="s">
         <v>129</v>
@@ -5162,16 +5162,16 @@
         <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C44" t="s">
         <v>131</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -5185,7 +5185,7 @@
         <v>532</v>
       </c>
       <c r="C45" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D45" t="s">
         <v>162</v>
@@ -5232,7 +5232,7 @@
         <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="C49" t="s">
         <v>134</v>
@@ -5272,10 +5272,10 @@
         <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="C51" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D51" t="s">
         <v>157</v>
@@ -5857,10 +5857,10 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="C87" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D87" t="s">
         <v>157</v>
@@ -5877,10 +5877,10 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="C88" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -5902,7 +5902,7 @@
         <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>997</v>
+        <v>527</v>
       </c>
       <c r="C90" t="s">
         <v>131</v>
@@ -5911,7 +5911,7 @@
         <v>144</v>
       </c>
       <c r="E90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F90">
         <v>2</v>
@@ -5962,7 +5962,7 @@
         <v>71</v>
       </c>
       <c r="B93" t="s">
-        <v>998</v>
+        <v>535</v>
       </c>
       <c r="C93" t="s">
         <v>134</v>
@@ -5971,7 +5971,7 @@
         <v>147</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93">
         <v>2</v>
@@ -6027,10 +6027,10 @@
         <v>74</v>
       </c>
       <c r="B97" t="s">
-        <v>961</v>
+        <v>941</v>
       </c>
       <c r="C97" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="D97" t="s">
         <v>135</v>
@@ -6202,16 +6202,16 @@
         <v>80</v>
       </c>
       <c r="B108" t="s">
-        <v>547</v>
+        <v>979</v>
       </c>
       <c r="C108" t="s">
         <v>146</v>
       </c>
       <c r="D108" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E108">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F108">
         <v>2</v>
@@ -6697,7 +6697,7 @@
         <v>103</v>
       </c>
       <c r="B138" t="s">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="C138" t="s">
         <v>126</v>
@@ -7039,7 +7039,7 @@
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>991</v>
+        <v>971</v>
       </c>
       <c r="E6">
         <v>0.6</v>
@@ -7056,7 +7056,7 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="E7">
         <v>0.6</v>
@@ -7084,16 +7084,16 @@
         <v>37</v>
       </c>
       <c r="B9">
-        <v>148</v>
+        <v>14633</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7101,16 +7101,16 @@
         <v>37</v>
       </c>
       <c r="B10">
-        <v>14633</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E10">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7192,7 +7192,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>995</v>
+        <v>975</v>
       </c>
       <c r="E15">
         <v>0.6</v>
@@ -7237,16 +7237,16 @@
         <v>44</v>
       </c>
       <c r="B18">
-        <v>148</v>
+        <v>14633</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7254,16 +7254,16 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>14633</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E19">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7345,7 +7345,7 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="E24">
         <v>0.6</v>
@@ -7611,16 +7611,16 @@
         <v>90</v>
       </c>
       <c r="B40">
-        <v>14686</v>
+        <v>506</v>
       </c>
       <c r="C40" t="s">
         <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>997</v>
+        <v>527</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -7628,16 +7628,16 @@
         <v>90</v>
       </c>
       <c r="B41">
-        <v>506</v>
+        <v>14686</v>
       </c>
       <c r="C41" t="s">
         <v>68</v>
       </c>
       <c r="D41" t="s">
-        <v>527</v>
+        <v>977</v>
       </c>
       <c r="E41">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -7679,16 +7679,16 @@
         <v>93</v>
       </c>
       <c r="B44">
-        <v>2081</v>
+        <v>10658</v>
       </c>
       <c r="C44" t="s">
         <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>998</v>
+        <v>535</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -7696,16 +7696,16 @@
         <v>93</v>
       </c>
       <c r="B45">
-        <v>10658</v>
+        <v>2081</v>
       </c>
       <c r="C45" t="s">
         <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>535</v>
+        <v>978</v>
       </c>
       <c r="E45">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -7747,16 +7747,16 @@
         <v>108</v>
       </c>
       <c r="B48">
-        <v>7155</v>
+        <v>18920</v>
       </c>
       <c r="C48" t="s">
         <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>547</v>
+        <v>979</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -7764,16 +7764,16 @@
         <v>108</v>
       </c>
       <c r="B49">
-        <v>18920</v>
+        <v>7155</v>
       </c>
       <c r="C49" t="s">
         <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>999</v>
+        <v>547</v>
       </c>
       <c r="E49">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -8279,7 +8279,7 @@
         <v>568</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>570</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -8296,14 +8296,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>864</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8313,17 +8313,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>867</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1048</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -8333,37 +8333,37 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>868</v>
+        <v>850</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1049</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>870</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>871</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -8373,7 +8373,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -8383,22 +8383,22 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>982</v>
+        <v>962</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>874</v>
+        <v>856</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -8408,22 +8408,22 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>877</v>
+        <v>859</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -8433,22 +8433,22 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1050</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>983</v>
+        <v>963</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -8463,22 +8463,22 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1051</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8488,22 +8488,22 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>885</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1052</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>887</v>
+        <v>868</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -8513,27 +8513,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1053</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>885</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>984</v>
+        <v>964</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -8548,22 +8548,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1054</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -8573,22 +8573,22 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -8598,32 +8598,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>901</v>
+        <v>882</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -8638,17 +8638,17 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -8658,22 +8658,22 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>907</v>
+        <v>888</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -8683,32 +8683,32 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>909</v>
+        <v>890</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>910</v>
+        <v>891</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>911</v>
+        <v>892</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>913</v>
+        <v>894</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -8728,22 +8728,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>916</v>
+        <v>897</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -8753,22 +8753,22 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>917</v>
+        <v>898</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -8778,32 +8778,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>920</v>
+        <v>901</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>986</v>
+        <v>966</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>921</v>
+        <v>902</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>922</v>
+        <v>903</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -8818,22 +8818,22 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>923</v>
+        <v>904</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -8843,22 +8843,22 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>926</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
     </row>
     <row r="114" spans="1:1">
@@ -8868,27 +8868,27 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -8903,22 +8903,22 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>935</v>
+        <v>915</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>937</v>
+        <v>917</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -8928,22 +8928,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>939</v>
+        <v>919</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -8953,32 +8953,32 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>943</v>
+        <v>923</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -8993,17 +8993,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1057</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -9013,22 +9013,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -9038,22 +9038,22 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>957</v>
+        <v>937</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1058</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -9085,14 +9085,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>771</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -9102,17 +9102,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1037</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -9122,37 +9122,37 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>774</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1038</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -9162,7 +9162,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9172,22 +9172,22 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -9197,22 +9197,22 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -9222,22 +9222,22 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1039</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -9252,22 +9252,22 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1040</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -9277,22 +9277,22 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>791</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1041</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -9302,27 +9302,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1042</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>791</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -9337,22 +9337,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1043</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -9362,22 +9362,22 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -9387,32 +9387,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -9427,17 +9427,17 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -9447,22 +9447,22 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>813</v>
+        <v>797</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -9472,32 +9472,32 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>816</v>
+        <v>800</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>820</v>
+        <v>804</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -9517,22 +9517,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>822</v>
+        <v>806</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -9547,12 +9547,12 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>823</v>
+        <v>807</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>824</v>
+        <v>808</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -9567,32 +9567,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>825</v>
+        <v>809</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>981</v>
+        <v>961</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -9607,22 +9607,22 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -9632,22 +9632,22 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>832</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>833</v>
+        <v>816</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>834</v>
+        <v>817</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>835</v>
+        <v>818</v>
       </c>
     </row>
     <row r="114" spans="1:1">
@@ -9657,27 +9657,27 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>837</v>
+        <v>820</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>838</v>
+        <v>821</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>840</v>
+        <v>823</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -9692,22 +9692,22 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>841</v>
+        <v>824</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>842</v>
+        <v>825</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>843</v>
+        <v>826</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>844</v>
+        <v>827</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -9717,22 +9717,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>846</v>
+        <v>829</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>847</v>
+        <v>830</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>848</v>
+        <v>831</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -9742,32 +9742,32 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>850</v>
+        <v>833</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>852</v>
+        <v>835</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -9782,17 +9782,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1046</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>856</v>
+        <v>839</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -9802,22 +9802,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -9827,22 +9827,22 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>861</v>
+        <v>844</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>863</v>
+        <v>846</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1047</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -9874,14 +9874,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>739</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -9891,12 +9891,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -9921,7 +9921,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9951,7 +9951,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9986,12 +9986,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -10021,7 +10021,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1032</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -10066,7 +10066,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>745</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -10081,7 +10081,7 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -10091,17 +10091,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1033</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>745</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -10111,7 +10111,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -10131,7 +10131,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -10141,7 +10141,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -10156,7 +10156,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -10181,7 +10181,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -10201,7 +10201,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -10216,7 +10216,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -10251,7 +10251,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -10311,7 +10311,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1025</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -10346,7 +10346,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -10356,7 +10356,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -10376,7 +10376,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -10396,7 +10396,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -10421,7 +10421,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>759</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -10431,7 +10431,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -10446,17 +10446,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -10506,7 +10506,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -10516,12 +10516,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -10531,7 +10531,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -10551,7 +10551,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -10571,7 +10571,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1035</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -10606,7 +10606,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -10616,7 +10616,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -10631,7 +10631,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1036</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -10663,14 +10663,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>730</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -10680,17 +10680,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1018</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -10705,12 +10705,12 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1029</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -10725,7 +10725,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -10740,7 +10740,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -10750,7 +10750,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -10775,12 +10775,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -10810,12 +10810,12 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1020</v>
+        <v>996</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -10845,7 +10845,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1021</v>
+        <v>997</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -10855,7 +10855,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>702</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -10865,12 +10865,12 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -10880,27 +10880,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>702</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -10915,22 +10915,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -10945,7 +10945,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -10970,7 +10970,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -10990,7 +10990,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -11005,7 +11005,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -11040,7 +11040,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -11060,7 +11060,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -11095,22 +11095,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -11120,7 +11120,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -11135,7 +11135,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -11145,7 +11145,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -11155,7 +11155,7 @@
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
     </row>
     <row r="100" spans="1:1">
@@ -11165,7 +11165,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -11185,7 +11185,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -11210,7 +11210,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>717</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -11220,7 +11220,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -11235,17 +11235,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -11295,7 +11295,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -11305,12 +11305,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -11320,7 +11320,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -11335,12 +11335,12 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -11360,7 +11360,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1031</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -11395,7 +11395,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -11405,7 +11405,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -11415,12 +11415,12 @@
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1028</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -11452,14 +11452,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>695</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -11469,17 +11469,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1018</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -11494,12 +11494,12 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1019</v>
+        <v>995</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -11529,7 +11529,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -11539,7 +11539,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>967</v>
+        <v>947</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -11564,12 +11564,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -11599,12 +11599,12 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1020</v>
+        <v>996</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -11634,7 +11634,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1021</v>
+        <v>997</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -11644,7 +11644,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>702</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -11654,12 +11654,12 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1022</v>
+        <v>998</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -11669,27 +11669,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>702</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -11704,22 +11704,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -11734,7 +11734,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -11759,7 +11759,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -11779,7 +11779,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -11794,7 +11794,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -11829,7 +11829,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -11849,7 +11849,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -11889,17 +11889,17 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -11909,7 +11909,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -11924,7 +11924,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -11934,7 +11934,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -11944,7 +11944,7 @@
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
     </row>
     <row r="100" spans="1:1">
@@ -11954,7 +11954,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -11974,7 +11974,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -11999,7 +11999,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>717</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -12009,7 +12009,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -12024,17 +12024,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -12084,7 +12084,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -12094,12 +12094,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -12109,7 +12109,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -12124,12 +12124,12 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -12149,7 +12149,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1027</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -12184,7 +12184,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -12194,7 +12194,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -12209,7 +12209,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1028</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -12241,14 +12241,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>601</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -12258,17 +12258,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1007</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -12278,37 +12278,37 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1008</v>
+        <v>986</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -12318,7 +12318,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -12328,22 +12328,22 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>962</v>
+        <v>942</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -12353,22 +12353,22 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -12378,22 +12378,22 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1009</v>
+        <v>987</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>963</v>
+        <v>943</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -12408,22 +12408,22 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1010</v>
+        <v>988</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -12433,22 +12433,22 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>622</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1011</v>
+        <v>989</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -12458,27 +12458,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>622</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>964</v>
+        <v>944</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -12493,22 +12493,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -12518,22 +12518,22 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -12543,32 +12543,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -12583,17 +12583,17 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -12603,22 +12603,22 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -12628,32 +12628,32 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -12673,22 +12673,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -12698,22 +12698,22 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1014</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1015</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -12723,32 +12723,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -12763,22 +12763,22 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -12788,22 +12788,22 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>663</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="114" spans="1:1">
@@ -12813,27 +12813,27 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -12848,22 +12848,22 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -12873,22 +12873,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -12898,32 +12898,32 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -12938,17 +12938,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1016</v>
+        <v>992</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -12958,22 +12958,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -12983,22 +12983,22 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1017</v>
+        <v>993</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -13811,14 +13811,14 @@
     <col min="1" max="1" width="128.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="255">
+    <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -13833,7 +13833,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -13858,7 +13858,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -13888,7 +13888,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -13928,7 +13928,7 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -13958,7 +13958,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1001</v>
+        <v>981</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -14003,7 +14003,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>577</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -14018,7 +14018,7 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -14028,17 +14028,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1002</v>
+        <v>982</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>577</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -14048,7 +14048,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -14068,7 +14068,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -14078,7 +14078,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -14093,7 +14093,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -14118,7 +14118,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -14138,7 +14138,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -14153,7 +14153,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -14188,7 +14188,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -14208,7 +14208,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -14248,7 +14248,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -14268,7 +14268,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1003</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -14283,7 +14283,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1004</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -14313,7 +14313,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -14333,7 +14333,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -14358,7 +14358,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>591</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -14383,17 +14383,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -14443,7 +14443,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -14453,12 +14453,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -14488,7 +14488,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -14508,7 +14508,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1005</v>
+        <v>983</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -14543,7 +14543,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -14553,7 +14553,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -14568,7 +14568,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
     </row>
     <row r="153" spans="1:1">

--- a/output/【河洛話注音】京口北固亭懷古.xlsx
+++ b/output/【河洛話注音】京口北固亭懷古.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEC4E11-D487-4610-87D3-1F5FEA138127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44D81D9-F14B-4569-BF44-3281AB812C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
   </bookViews>
   <sheets>
     <sheet name="閩拼拼音" sheetId="45" r:id="rId1"/>

--- a/output/【河洛話注音】京口北固亭懷古.xlsx
+++ b/output/【河洛話注音】京口北固亭懷古.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44D81D9-F14B-4569-BF44-3281AB812C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFED3891-786C-450A-947B-8DC9A9720071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{E693FAA9-3885-7942-89D0-D7B6B37754A0}"/>
   </bookViews>
   <sheets>
     <sheet name="閩拼拼音" sheetId="45" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="1062">
   <si>
     <t>《</t>
   </si>
@@ -1700,9 +1700,6 @@
     <t>si3</t>
   </si>
   <si>
-    <t>biong5</t>
-  </si>
-  <si>
     <t>Øiu5</t>
   </si>
   <si>
@@ -2892,9 +2889,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄑㄧㄢ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄑㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㄨㄧ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -2907,9 +2901,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhian&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhui&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -2922,9 +2913,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshian&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshí&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshui&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -2937,9 +2925,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chian1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chi2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chui1&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -2952,9 +2937,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;千&lt;/rb&gt;&lt;rt&gt;chian1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄑㄧㄢ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rt&gt;chi2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄑㄧˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;吹&lt;/rb&gt;&lt;rt&gt;chui1&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㄨㄧ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -3000,9 +2982,6 @@
     <t>su1</t>
   </si>
   <si>
-    <t>bong7</t>
-  </si>
-  <si>
     <t>ping5</t>
   </si>
   <si>
@@ -3156,9 +3135,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍二時&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;公七門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㆲ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -3168,9 +3144,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㆲ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hòng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -3180,18 +3153,12 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sú&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bōng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;封&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hīong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;sǔ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbông&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hong3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -3201,9 +3168,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bong7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;風&lt;/rb&gt;&lt;rt&gt;hong3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆲ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -3211,9 +3175,6 @@
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;胥&lt;/rb&gt;&lt;rt&gt;su2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄙㄨˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rt&gt;bong7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㆲ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t>https://img.guwenxuexi.com/wp-content/uploads/2017/05/4-7.jpg</t>
@@ -3287,6 +3248,54 @@
   &lt;/a&gt;
 &lt;/div&gt;
 </t>
+  </si>
+  <si>
+    <t>chu3</t>
+  </si>
+  <si>
+    <t>biong7</t>
+  </si>
+  <si>
+    <t>bong5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;艍三出&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;恭七門&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄘㄨ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㆠㄧㆲ˫&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chhù&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bīong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;tshù&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;cù&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bbîong&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;chu3&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;biong7&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;處&lt;/rb&gt;&lt;rt&gt;chu3&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄘㄨ˪&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;望&lt;/rb&gt;&lt;rt&gt;biong7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㆠㄧㆲ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
 </sst>
 </file>
@@ -4518,7 +4527,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -4557,7 +4566,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="C7" t="s">
         <v>124</v>
@@ -4692,10 +4701,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
+        <v>937</v>
+      </c>
+      <c r="C16" t="s">
         <v>938</v>
-      </c>
-      <c r="C16" t="s">
-        <v>939</v>
       </c>
       <c r="D16" t="s">
         <v>139</v>
@@ -4902,10 +4911,10 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C28" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="D28" t="s">
         <v>160</v>
@@ -4922,16 +4931,16 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>525</v>
+        <v>1046</v>
       </c>
       <c r="C29" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -5012,13 +5021,13 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C35" t="s">
         <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -5077,7 +5086,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="C39" t="s">
         <v>539</v>
@@ -5142,7 +5151,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C43" t="s">
         <v>129</v>
@@ -5185,7 +5194,7 @@
         <v>532</v>
       </c>
       <c r="C45" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D45" t="s">
         <v>162</v>
@@ -5232,7 +5241,7 @@
         <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C49" t="s">
         <v>134</v>
@@ -5272,10 +5281,10 @@
         <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C51" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D51" t="s">
         <v>157</v>
@@ -5857,10 +5866,10 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C87" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D87" t="s">
         <v>157</v>
@@ -5877,10 +5886,10 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C88" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -6027,10 +6036,10 @@
         <v>74</v>
       </c>
       <c r="B97" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C97" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D97" t="s">
         <v>135</v>
@@ -6202,13 +6211,13 @@
         <v>80</v>
       </c>
       <c r="B108" t="s">
-        <v>979</v>
+        <v>1047</v>
       </c>
       <c r="C108" t="s">
         <v>146</v>
       </c>
       <c r="D108" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E108">
         <v>7</v>
@@ -6242,7 +6251,7 @@
         <v>82</v>
       </c>
       <c r="B110" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C110" t="s">
         <v>519</v>
@@ -6307,7 +6316,7 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C114" t="s">
         <v>131</v>
@@ -6347,7 +6356,7 @@
         <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C116" t="s">
         <v>539</v>
@@ -6522,7 +6531,7 @@
         <v>95</v>
       </c>
       <c r="B127" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C127" t="s">
         <v>134</v>
@@ -6542,7 +6551,7 @@
         <v>96</v>
       </c>
       <c r="B128" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C128" t="s">
         <v>131</v>
@@ -6567,7 +6576,7 @@
         <v>97</v>
       </c>
       <c r="B130" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C130" t="s">
         <v>519</v>
@@ -6627,7 +6636,7 @@
         <v>100</v>
       </c>
       <c r="B133" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C133" t="s">
         <v>519</v>
@@ -6647,7 +6656,7 @@
         <v>101</v>
       </c>
       <c r="B134" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C134" t="s">
         <v>134</v>
@@ -6697,7 +6706,7 @@
         <v>103</v>
       </c>
       <c r="B138" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="C138" t="s">
         <v>126</v>
@@ -6822,7 +6831,7 @@
         <v>110</v>
       </c>
       <c r="B145" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C145" t="s">
         <v>519</v>
@@ -6907,7 +6916,7 @@
         <v>114</v>
       </c>
       <c r="B150" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C150" t="s">
         <v>131</v>
@@ -6999,16 +7008,16 @@
         <v>29</v>
       </c>
       <c r="B4">
-        <v>10647</v>
+        <v>15614</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>525</v>
+        <v>1046</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7016,7 +7025,7 @@
         <v>29</v>
       </c>
       <c r="B5">
-        <v>15614</v>
+        <v>10647</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
@@ -7039,7 +7048,7 @@
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="E6">
         <v>0.6</v>
@@ -7056,7 +7065,7 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="E7">
         <v>0.6</v>
@@ -7192,7 +7201,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="E15">
         <v>0.6</v>
@@ -7345,7 +7354,7 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="E24">
         <v>0.6</v>
@@ -7634,7 +7643,7 @@
         <v>68</v>
       </c>
       <c r="D41" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7702,7 +7711,7 @@
         <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7753,10 +7762,10 @@
         <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>979</v>
+        <v>1047</v>
       </c>
       <c r="E48">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -7770,10 +7779,10 @@
         <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>547</v>
+        <v>1048</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -7821,7 +7830,7 @@
         <v>82</v>
       </c>
       <c r="D52" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -7838,7 +7847,7 @@
         <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -7855,7 +7864,7 @@
         <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -7906,7 +7915,7 @@
         <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -7923,7 +7932,7 @@
         <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -8042,7 +8051,7 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -8059,7 +8068,7 @@
         <v>112</v>
       </c>
       <c r="D66" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -8076,7 +8085,7 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -8127,7 +8136,7 @@
         <v>114</v>
       </c>
       <c r="D70" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E70">
         <v>0.6</v>
@@ -8244,42 +8253,42 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
@@ -8298,12 +8307,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8313,17 +8322,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -8333,37 +8342,37 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -8373,7 +8382,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -8383,22 +8392,22 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -8408,22 +8417,22 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -8433,22 +8442,22 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>963</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -8463,22 +8472,22 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8488,22 +8497,22 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -8513,27 +8522,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -8548,22 +8557,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -8573,22 +8582,22 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -8598,32 +8607,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -8638,17 +8647,17 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -8658,22 +8667,22 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -8683,32 +8692,32 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -8728,22 +8737,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -8753,22 +8762,22 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -8778,32 +8787,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -8818,22 +8827,22 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -8843,22 +8852,22 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="114" spans="1:1">
@@ -8868,27 +8877,27 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -8903,22 +8912,22 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -8928,22 +8937,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -8953,32 +8962,32 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -8993,17 +9002,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -9013,22 +9022,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -9038,22 +9047,22 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -9087,12 +9096,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -9102,17 +9111,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -9122,37 +9131,37 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -9162,7 +9171,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9172,22 +9181,22 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -9197,22 +9206,22 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -9222,22 +9231,22 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>958</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -9252,22 +9261,22 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -9277,22 +9286,22 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -9302,27 +9311,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -9337,22 +9346,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -9362,22 +9371,22 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -9387,32 +9396,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -9427,17 +9436,17 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -9447,22 +9456,22 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -9472,32 +9481,32 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -9517,22 +9526,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -9542,22 +9551,22 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -9567,32 +9576,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -9607,22 +9616,22 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -9632,22 +9641,22 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="114" spans="1:1">
@@ -9657,27 +9666,27 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -9692,22 +9701,22 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -9717,22 +9726,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -9742,32 +9751,32 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -9782,17 +9791,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -9802,22 +9811,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -9827,22 +9836,22 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -9876,12 +9885,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -9891,12 +9900,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -9921,7 +9930,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9951,7 +9960,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9986,12 +9995,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -10021,12 +10030,12 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>418</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -10066,7 +10075,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -10081,7 +10090,7 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -10091,17 +10100,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -10111,7 +10120,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -10131,7 +10140,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -10141,7 +10150,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -10156,7 +10165,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -10181,7 +10190,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -10201,7 +10210,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -10216,7 +10225,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -10251,7 +10260,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -10271,7 +10280,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -10311,7 +10320,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -10331,7 +10340,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -10346,7 +10355,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -10356,7 +10365,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -10376,7 +10385,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -10396,7 +10405,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -10421,7 +10430,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1042</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -10431,7 +10440,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -10446,17 +10455,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -10506,7 +10515,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -10516,12 +10525,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -10531,7 +10540,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -10551,7 +10560,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -10571,7 +10580,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -10606,7 +10615,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -10616,7 +10625,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -10631,7 +10640,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -10665,12 +10674,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1055</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -10680,17 +10689,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -10705,12 +10714,12 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -10725,7 +10734,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -10740,7 +10749,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -10750,7 +10759,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -10775,12 +10784,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -10810,12 +10819,12 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>953</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -10845,7 +10854,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -10855,7 +10864,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -10865,12 +10874,12 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -10880,27 +10889,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -10915,22 +10924,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -10945,7 +10954,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -10970,7 +10979,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -10990,7 +10999,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -11005,7 +11014,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -11040,7 +11049,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -11060,7 +11069,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -11095,22 +11104,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -11120,7 +11129,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -11135,7 +11144,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -11145,7 +11154,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -11155,7 +11164,7 @@
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
     </row>
     <row r="100" spans="1:1">
@@ -11165,7 +11174,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -11185,7 +11194,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -11210,7 +11219,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1039</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -11220,7 +11229,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -11235,17 +11244,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -11295,7 +11304,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -11305,12 +11314,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -11320,7 +11329,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -11335,12 +11344,12 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -11360,7 +11369,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -11395,7 +11404,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -11405,7 +11414,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -11415,12 +11424,12 @@
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -11454,12 +11463,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1054</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -11469,17 +11478,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -11494,12 +11503,12 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -11529,7 +11538,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -11539,7 +11548,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -11564,12 +11573,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -11599,12 +11608,12 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>948</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -11634,7 +11643,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -11644,7 +11653,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -11654,12 +11663,12 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -11669,27 +11678,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -11704,22 +11713,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -11734,7 +11743,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -11759,7 +11768,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -11779,7 +11788,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -11794,7 +11803,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -11829,7 +11838,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -11849,7 +11858,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -11889,17 +11898,17 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -11909,7 +11918,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -11924,7 +11933,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -11934,7 +11943,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -11944,7 +11953,7 @@
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="100" spans="1:1">
@@ -11954,7 +11963,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -11974,7 +11983,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -11999,7 +12008,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1039</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -12009,7 +12018,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -12024,17 +12033,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -12084,7 +12093,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -12094,12 +12103,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -12109,7 +12118,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -12124,12 +12133,12 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -12149,7 +12158,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -12184,7 +12193,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -12194,7 +12203,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -12209,7 +12218,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -12243,12 +12252,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -12258,17 +12267,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -12278,37 +12287,37 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -12318,7 +12327,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -12328,22 +12337,22 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -12353,22 +12362,22 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -12378,22 +12387,22 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>943</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -12408,22 +12417,22 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -12433,22 +12442,22 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -12458,27 +12467,27 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -12493,22 +12502,22 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -12518,22 +12527,22 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -12543,32 +12552,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -12583,17 +12592,17 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -12603,22 +12612,22 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -12628,32 +12637,32 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -12673,22 +12682,22 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -12698,22 +12707,22 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -12723,32 +12732,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -12763,22 +12772,22 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -12788,22 +12797,22 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1035</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114" spans="1:1">
@@ -12813,27 +12822,27 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -12848,22 +12857,22 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -12873,22 +12882,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -12898,32 +12907,32 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -12938,17 +12947,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -12958,22 +12967,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -12983,22 +12992,22 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -13813,12 +13822,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -13833,7 +13842,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -13858,7 +13867,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -13888,7 +13897,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -13928,7 +13937,7 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -13958,12 +13967,12 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>232</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -14003,7 +14012,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -14018,7 +14027,7 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -14028,17 +14037,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -14048,7 +14057,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -14068,7 +14077,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -14078,7 +14087,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -14093,7 +14102,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -14118,7 +14127,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -14138,7 +14147,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -14153,7 +14162,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -14188,7 +14197,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -14208,7 +14217,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -14248,7 +14257,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -14268,7 +14277,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -14283,7 +14292,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -14313,7 +14322,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -14333,7 +14342,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -14358,7 +14367,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1031</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -14383,17 +14392,17 @@
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -14443,7 +14452,7 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -14453,12 +14462,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -14488,7 +14497,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -14508,7 +14517,7 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -14543,7 +14552,7 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -14553,7 +14562,7 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -14568,7 +14577,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
     </row>
     <row r="153" spans="1:1">
